--- a/backend/signal_logs/2026-08-08/signals_2026-08-08.xlsx
+++ b/backend/signal_logs/2026-08-08/signals_2026-08-08.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1196,12 +1196,635 @@
           <t>NSE:M&amp;M26AUG3500CE</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:25:59</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1658</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1660</v>
+      </c>
+      <c r="I9" t="n">
+        <v>40</v>
+      </c>
+      <c r="J9" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="K9" t="n">
+        <v>51.68</v>
+      </c>
+      <c r="L9" t="n">
+        <v>58.69</v>
+      </c>
+      <c r="M9" t="n">
+        <v>68.04000000000001</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1250</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="S9" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>64.45999999999999</v>
+      </c>
+      <c r="U9" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NSE:AUROPHARMA26AUG1660CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:25:59</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>249.95</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="H10" t="n">
+        <v>250</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7575</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="S10" t="n">
+        <v>34</v>
+      </c>
+      <c r="T10" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="U10" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NSE:CROMPTON26AUG250PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:25:59</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>5725</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5700</v>
+      </c>
+      <c r="I11" t="n">
+        <v>160</v>
+      </c>
+      <c r="J11" t="n">
+        <v>112.67</v>
+      </c>
+      <c r="K11" t="n">
+        <v>202.26</v>
+      </c>
+      <c r="L11" t="n">
+        <v>227.63</v>
+      </c>
+      <c r="M11" t="n">
+        <v>261.44</v>
+      </c>
+      <c r="N11" t="n">
+        <v>312</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="S11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="U11" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>NSE:HEROMOTOCO26AUG5700CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:26:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>486.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="H12" t="n">
+        <v>485</v>
+      </c>
+      <c r="I12" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="K12" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="L12" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="M12" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3367</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="S12" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>74.51000000000001</v>
+      </c>
+      <c r="U12" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>NSE:JUBLFOOD26AUG485CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:26:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2265.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2260</v>
+      </c>
+      <c r="I13" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="J13" t="n">
+        <v>70.18000000000001</v>
+      </c>
+      <c r="K13" t="n">
+        <v>95.58</v>
+      </c>
+      <c r="L13" t="n">
+        <v>102.77</v>
+      </c>
+      <c r="M13" t="n">
+        <v>112.36</v>
+      </c>
+      <c r="N13" t="n">
+        <v>598</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="S13" t="n">
+        <v>37</v>
+      </c>
+      <c r="T13" t="n">
+        <v>61.07</v>
+      </c>
+      <c r="U13" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>NSE:BHARATFORG26AUG2260CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:26:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>818.05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="H14" t="n">
+        <v>820</v>
+      </c>
+      <c r="I14" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="K14" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="L14" t="n">
+        <v>34.36</v>
+      </c>
+      <c r="M14" t="n">
+        <v>39.68</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2109</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="S14" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>76.66</v>
+      </c>
+      <c r="U14" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>NSE:SONACOMS26AUG820CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:26:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3502</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I15" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>46.57</v>
+      </c>
+      <c r="K15" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>111.98</v>
+      </c>
+      <c r="M15" t="n">
+        <v>131.21</v>
+      </c>
+      <c r="N15" t="n">
+        <v>680</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="S15" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>73.26000000000001</v>
+      </c>
+      <c r="U15" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>NSE:M&amp;M26AUG3500CE</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-08/signals_2026-08-08.xlsx
+++ b/backend/signal_logs/2026-08-08/signals_2026-08-08.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1819,12 +1819,635 @@
           <t>NSE:M&amp;M26AUG3500CE</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:27:50</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1658</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1660</v>
+      </c>
+      <c r="I16" t="n">
+        <v>40</v>
+      </c>
+      <c r="J16" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="K16" t="n">
+        <v>51.68</v>
+      </c>
+      <c r="L16" t="n">
+        <v>58.69</v>
+      </c>
+      <c r="M16" t="n">
+        <v>68.04000000000001</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1250</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="S16" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>64.45999999999999</v>
+      </c>
+      <c r="U16" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>NSE:AUROPHARMA26AUG1660CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:27:50</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>249.95</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="H17" t="n">
+        <v>250</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="L17" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="M17" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7575</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="S17" t="n">
+        <v>34</v>
+      </c>
+      <c r="T17" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="U17" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>NSE:CROMPTON26AUG250PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:27:50</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>5725</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5700</v>
+      </c>
+      <c r="I18" t="n">
+        <v>160</v>
+      </c>
+      <c r="J18" t="n">
+        <v>112.67</v>
+      </c>
+      <c r="K18" t="n">
+        <v>202.26</v>
+      </c>
+      <c r="L18" t="n">
+        <v>227.63</v>
+      </c>
+      <c r="M18" t="n">
+        <v>261.44</v>
+      </c>
+      <c r="N18" t="n">
+        <v>312</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="S18" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="U18" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>NSE:HEROMOTOCO26AUG5700CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:27:50</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>486.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="H19" t="n">
+        <v>485</v>
+      </c>
+      <c r="I19" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="J19" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="K19" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="L19" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="M19" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3367</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="S19" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>74.51000000000001</v>
+      </c>
+      <c r="U19" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>NSE:JUBLFOOD26AUG485CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:27:50</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2265.2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2260</v>
+      </c>
+      <c r="I20" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="J20" t="n">
+        <v>70.18000000000001</v>
+      </c>
+      <c r="K20" t="n">
+        <v>95.58</v>
+      </c>
+      <c r="L20" t="n">
+        <v>102.77</v>
+      </c>
+      <c r="M20" t="n">
+        <v>112.36</v>
+      </c>
+      <c r="N20" t="n">
+        <v>598</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="S20" t="n">
+        <v>37</v>
+      </c>
+      <c r="T20" t="n">
+        <v>61.07</v>
+      </c>
+      <c r="U20" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>NSE:BHARATFORG26AUG2260CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:27:50</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>818.05</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="H21" t="n">
+        <v>820</v>
+      </c>
+      <c r="I21" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="K21" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="L21" t="n">
+        <v>34.36</v>
+      </c>
+      <c r="M21" t="n">
+        <v>39.68</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2109</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="S21" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>76.66</v>
+      </c>
+      <c r="U21" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>NSE:SONACOMS26AUG820CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:27:50</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>3502</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I22" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>46.57</v>
+      </c>
+      <c r="K22" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="L22" t="n">
+        <v>111.98</v>
+      </c>
+      <c r="M22" t="n">
+        <v>131.21</v>
+      </c>
+      <c r="N22" t="n">
+        <v>680</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="S22" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>73.26000000000001</v>
+      </c>
+      <c r="U22" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>NSE:M&amp;M26AUG3500CE</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-08/signals_2026-08-08.xlsx
+++ b/backend/signal_logs/2026-08-08/signals_2026-08-08.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2442,12 +2442,635 @@
           <t>NSE:M&amp;M26AUG3500CE</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:31:26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1658</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1660</v>
+      </c>
+      <c r="I23" t="n">
+        <v>40</v>
+      </c>
+      <c r="J23" t="n">
+        <v>26.91</v>
+      </c>
+      <c r="K23" t="n">
+        <v>51.68</v>
+      </c>
+      <c r="L23" t="n">
+        <v>58.69</v>
+      </c>
+      <c r="M23" t="n">
+        <v>68.04000000000001</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1250</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="S23" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T23" t="n">
+        <v>64.45999999999999</v>
+      </c>
+      <c r="U23" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>NSE:AUROPHARMA26AUG1660CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:31:26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CROMPTON</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>249.95</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="H24" t="n">
+        <v>250</v>
+      </c>
+      <c r="I24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K24" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="L24" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="M24" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="N24" t="n">
+        <v>7575</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="S24" t="n">
+        <v>34</v>
+      </c>
+      <c r="T24" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="U24" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>NSE:CROMPTON26AUG250PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:31:26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>5725</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5700</v>
+      </c>
+      <c r="I25" t="n">
+        <v>160</v>
+      </c>
+      <c r="J25" t="n">
+        <v>112.67</v>
+      </c>
+      <c r="K25" t="n">
+        <v>202.26</v>
+      </c>
+      <c r="L25" t="n">
+        <v>227.63</v>
+      </c>
+      <c r="M25" t="n">
+        <v>261.44</v>
+      </c>
+      <c r="N25" t="n">
+        <v>312</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="S25" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>75.66</v>
+      </c>
+      <c r="U25" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>NSE:HEROMOTOCO26AUG5700CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:31:26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>486.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="H26" t="n">
+        <v>485</v>
+      </c>
+      <c r="I26" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="J26" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="K26" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="L26" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="M26" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3367</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="S26" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>74.51000000000001</v>
+      </c>
+      <c r="U26" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>NSE:JUBLFOOD26AUG485CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:31:27</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2265.2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2260</v>
+      </c>
+      <c r="I27" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="J27" t="n">
+        <v>70.18000000000001</v>
+      </c>
+      <c r="K27" t="n">
+        <v>95.58</v>
+      </c>
+      <c r="L27" t="n">
+        <v>102.77</v>
+      </c>
+      <c r="M27" t="n">
+        <v>112.36</v>
+      </c>
+      <c r="N27" t="n">
+        <v>598</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="S27" t="n">
+        <v>37</v>
+      </c>
+      <c r="T27" t="n">
+        <v>61.07</v>
+      </c>
+      <c r="U27" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>NSE:BHARATFORG26AUG2260CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:31:27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>818.05</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="H28" t="n">
+        <v>820</v>
+      </c>
+      <c r="I28" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="J28" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="K28" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="L28" t="n">
+        <v>34.36</v>
+      </c>
+      <c r="M28" t="n">
+        <v>39.68</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2109</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="S28" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>76.66</v>
+      </c>
+      <c r="U28" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>NSE:SONACOMS26AUG820CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-08 20:31:27</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>3502</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I29" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>46.57</v>
+      </c>
+      <c r="K29" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="L29" t="n">
+        <v>111.98</v>
+      </c>
+      <c r="M29" t="n">
+        <v>131.21</v>
+      </c>
+      <c r="N29" t="n">
+        <v>680</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="S29" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>73.26000000000001</v>
+      </c>
+      <c r="U29" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>NSE:M&amp;M26AUG3500CE</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
